--- a/public/templates/student-import-template.xlsx
+++ b/public/templates/student-import-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5EA5E6-7ABC-4CA9-ABFC-31A6CC85AFE5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00B2D01-5E5D-41EA-B33A-2070513C7746}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>LRN</t>
   </si>
@@ -31,9 +31,6 @@
     <t>Last Name</t>
   </si>
   <si>
-    <t>Middle Name</t>
-  </si>
-  <si>
     <t>Grade</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
   </si>
   <si>
     <t>Ardina</t>
-  </si>
-  <si>
-    <t>John</t>
   </si>
   <si>
     <t>9</t>
@@ -471,22 +465,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
     <col min="2" max="2" width="19.875" customWidth="1"/>
-    <col min="3" max="6" width="16.875" customWidth="1"/>
-    <col min="7" max="7" width="45.875" customWidth="1"/>
-    <col min="8" max="8" width="16.875" customWidth="1"/>
-    <col min="9" max="9" width="21.875" customWidth="1"/>
-    <col min="10" max="10" width="22.875" customWidth="1"/>
-    <col min="11" max="11" width="20.875" customWidth="1"/>
-    <col min="12" max="12" width="23.875" customWidth="1"/>
-    <col min="13" max="13" width="30.875" customWidth="1"/>
+    <col min="3" max="5" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="45.875" customWidth="1"/>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="21.875" customWidth="1"/>
+    <col min="9" max="9" width="22.875" customWidth="1"/>
+    <col min="10" max="10" width="20.875" customWidth="1"/>
+    <col min="11" max="11" width="23.875" customWidth="1"/>
+    <col min="12" max="12" width="30.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -523,96 +517,87 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="J3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="K3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
       <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M1 A3:M3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A3:C3 D1:L1 D3:L3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>